--- a/output/graficos_dimensiones/comunal_e_matricula_a_2020_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2020_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:23</t>
+    <t xml:space="preserve">2026-09-10 01:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2020_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2020_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:37</t>
+    <t xml:space="preserve">2026-09-18 11:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2020_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2020_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:33</t>
+    <t xml:space="preserve">2026-09-23 15:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2020_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2020_o_higgins.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Litueche</t>
   </si>
   <si>
-    <t xml:space="preserve">Marchihue</t>
+    <t xml:space="preserve">Marchigüe</t>
   </si>
   <si>
     <t xml:space="preserve">Navidad</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:39</t>
+    <t xml:space="preserve">2026-10-04 10:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2020_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2020_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:48</t>
+    <t xml:space="preserve">2026-10-05 16:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1516,7 +1516,7 @@
         <v>87.31</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>39.35</v>
+        <v>39.36</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>68.08</v>
